--- a/data/trans_dic/P23_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P23_R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,37; 44,47</t>
+          <t>32,2; 43,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,91; 45,08</t>
+          <t>32,81; 44,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,92; 41,73</t>
+          <t>30,84; 42,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,58; 34,11</t>
+          <t>21,2; 33,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,64; 30,99</t>
+          <t>19,53; 30,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,0; 40,5</t>
+          <t>28,04; 39,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,08; 31,66</t>
+          <t>21,05; 30,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,91; 26,77</t>
+          <t>18,78; 26,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,68; 35,76</t>
+          <t>27,6; 35,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,2; 40,92</t>
+          <t>32,01; 40,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,99; 34,7</t>
+          <t>27,21; 35,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,45; 28,84</t>
+          <t>21,34; 29,22</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,49; 40,25</t>
+          <t>31,51; 40,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,37; 44,06</t>
+          <t>34,51; 44,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,31; 46,42</t>
+          <t>36,66; 45,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,2; 30,98</t>
+          <t>21,41; 31,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,12; 26,38</t>
+          <t>18,64; 26,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,74; 32,29</t>
+          <t>23,96; 32,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,05; 31,57</t>
+          <t>23,09; 31,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,45; 22,75</t>
+          <t>16,21; 22,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,98; 31,91</t>
+          <t>26,16; 31,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,61; 36,92</t>
+          <t>30,5; 36,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,25; 37,58</t>
+          <t>31,25; 37,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,51; 25,31</t>
+          <t>19,77; 25,82</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,85; 48,88</t>
+          <t>36,75; 48,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,4; 44,29</t>
+          <t>33,58; 44,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,3; 35,14</t>
+          <t>25,69; 35,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,3; 28,62</t>
+          <t>18,94; 28,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,67; 33,25</t>
+          <t>23,34; 32,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,01; 30,83</t>
+          <t>20,92; 30,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,01; 29,41</t>
+          <t>19,92; 29,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,27; 22,18</t>
+          <t>14,95; 22,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,67; 39,04</t>
+          <t>31,64; 39,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,06; 35,57</t>
+          <t>28,2; 35,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,78; 30,49</t>
+          <t>23,99; 30,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,23; 23,61</t>
+          <t>18,13; 23,81</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,05; 50,85</t>
+          <t>40,13; 50,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,1; 36,51</t>
+          <t>27,02; 36,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,1; 43,55</t>
+          <t>32,88; 43,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,69; 31,34</t>
+          <t>18,69; 31,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,23; 31,12</t>
+          <t>22,15; 31,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,85; 31,13</t>
+          <t>21,96; 31,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,33; 33,23</t>
+          <t>23,83; 33,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 20,75</t>
+          <t>9,2; 20,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,25; 39,31</t>
+          <t>32,02; 39,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,6; 32,14</t>
+          <t>25,63; 32,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,41; 36,39</t>
+          <t>29,21; 36,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,73; 23,25</t>
+          <t>13,7; 23,04</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,76; 45,95</t>
+          <t>31,61; 45,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,56; 49,27</t>
+          <t>34,42; 48,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,8; 47,87</t>
+          <t>33,42; 46,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,85; 24,31</t>
+          <t>14,77; 24,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,3; 33,92</t>
+          <t>21,56; 34,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,74; 36,85</t>
+          <t>23,79; 36,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,61; 32,33</t>
+          <t>20,53; 31,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,62; 17,81</t>
+          <t>11,27; 17,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,28; 37,8</t>
+          <t>28,41; 37,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,46; 41,12</t>
+          <t>30,97; 40,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28,71; 37,78</t>
+          <t>28,57; 37,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,58; 19,37</t>
+          <t>13,75; 19,68</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,88; 52,22</t>
+          <t>39,67; 51,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,93; 36,46</t>
+          <t>24,57; 35,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27,82; 39,66</t>
+          <t>28,32; 39,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,13; 33,09</t>
+          <t>22,75; 32,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,34; 28,07</t>
+          <t>18,32; 28,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,24; 29,55</t>
+          <t>19,34; 29,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,38; 31,89</t>
+          <t>21,64; 32,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,05; 22,77</t>
+          <t>14,98; 23,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30,31; 38,18</t>
+          <t>30,2; 38,12</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23,45; 30,67</t>
+          <t>23,28; 30,99</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,35; 33,99</t>
+          <t>26,35; 33,87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,2; 26,49</t>
+          <t>20,25; 26,64</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,25; 40,96</t>
+          <t>33,08; 41,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>34,83; 42,51</t>
+          <t>34,45; 42,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,37; 33,77</t>
+          <t>26,48; 33,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,28; 32,98</t>
+          <t>23,57; 32,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,84; 28,47</t>
+          <t>21,87; 28,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,96; 31,24</t>
+          <t>24,02; 30,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,67; 28,69</t>
+          <t>21,8; 28,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,37; 25,03</t>
+          <t>8,74; 24,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28,37; 33,56</t>
+          <t>28,33; 33,77</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,4; 35,81</t>
+          <t>30,09; 35,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25,06; 30,06</t>
+          <t>25,13; 29,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,58; 26,6</t>
+          <t>13,92; 26,72</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>36,49; 43,35</t>
+          <t>36,41; 43,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>32,34; 39,35</t>
+          <t>32,49; 39,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,42; 36,69</t>
+          <t>29,25; 36,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,89; 28,0</t>
+          <t>8,91; 28,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,76; 26,0</t>
+          <t>19,94; 25,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,33; 28,54</t>
+          <t>22,67; 28,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,93; 29,23</t>
+          <t>22,89; 28,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,35; 19,2</t>
+          <t>14,48; 19,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28,85; 33,5</t>
+          <t>28,82; 33,52</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28,11; 32,81</t>
+          <t>28,04; 32,73</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27,15; 31,84</t>
+          <t>26,96; 31,55</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,51; 22,18</t>
+          <t>11,18; 22,23</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38,0; 41,57</t>
+          <t>38,25; 41,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35,21; 38,77</t>
+          <t>35,12; 38,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32,99; 36,39</t>
+          <t>32,98; 36,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,25; 26,8</t>
+          <t>19,06; 26,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23,23; 26,21</t>
+          <t>23,11; 25,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,37; 28,5</t>
+          <t>25,46; 28,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,6; 27,56</t>
+          <t>24,57; 27,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,36; 19,5</t>
+          <t>14,79; 19,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30,89; 33,31</t>
+          <t>30,93; 33,33</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30,6; 32,99</t>
+          <t>30,69; 32,98</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29,07; 31,37</t>
+          <t>29,08; 31,37</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,1; 22,57</t>
+          <t>17,91; 22,56</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>88381; 121418</t>
+          <t>87907; 119139</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97012; 132861</t>
+          <t>96690; 130505</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87879; 122585</t>
+          <t>90606; 124241</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67208; 106245</t>
+          <t>66034; 103323</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>51223; 80841</t>
+          <t>50942; 80075</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80428; 116333</t>
+          <t>80556; 113738</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60864; 91416</t>
+          <t>60767; 88898</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>54768; 77529</t>
+          <t>54381; 77170</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>147792; 190904</t>
+          <t>147347; 190893</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>187388; 238150</t>
+          <t>186289; 235848</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>157201; 202125</t>
+          <t>158516; 204488</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>128946; 173328</t>
+          <t>128251; 175631</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>154935; 198022</t>
+          <t>155028; 199077</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>178781; 222752</t>
+          <t>174470; 223069</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>187173; 232909</t>
+          <t>183921; 230535</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>109896; 160588</t>
+          <t>110963; 165244</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>96375; 132951</t>
+          <t>93952; 131694</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>124331; 169100</t>
+          <t>125472; 168456</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>120089; 164421</t>
+          <t>120289; 163533</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84719; 117159</t>
+          <t>83493; 116780</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>258740; 317840</t>
+          <t>260527; 317720</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>315028; 379994</t>
+          <t>313924; 374922</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>319532; 384295</t>
+          <t>319574; 379528</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>201630; 261580</t>
+          <t>204287; 266833</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>120687; 155868</t>
+          <t>117184; 153800</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>108240; 143519</t>
+          <t>108827; 145311</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80584; 111956</t>
+          <t>81827; 113817</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61003; 90465</t>
+          <t>59875; 88508</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>79385; 111539</t>
+          <t>78280; 110217</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71428; 104818</t>
+          <t>71149; 104397</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67302; 98919</t>
+          <t>66983; 98032</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>53317; 77451</t>
+          <t>52181; 77235</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>207202; 255426</t>
+          <t>207027; 255813</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>186318; 236197</t>
+          <t>187291; 236096</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>155752; 199656</t>
+          <t>157093; 201232</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>121274; 157059</t>
+          <t>120589; 158363</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>143632; 182401</t>
+          <t>143928; 180536</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>97606; 136539</t>
+          <t>101062; 137540</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>122442; 161134</t>
+          <t>121648; 160332</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58427; 97959</t>
+          <t>58406; 97273</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>82584; 115588</t>
+          <t>82288; 115301</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>84980; 121095</t>
+          <t>85416; 120556</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90068; 128282</t>
+          <t>91976; 127693</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44651; 98698</t>
+          <t>43776; 97946</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>235453; 286978</t>
+          <t>233758; 286602</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>195320; 245185</t>
+          <t>195505; 247175</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>222348; 275071</t>
+          <t>220847; 275846</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>108253; 183309</t>
+          <t>107978; 181652</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>64570; 93419</t>
+          <t>64267; 93207</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73480; 104750</t>
+          <t>73177; 103060</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71402; 101117</t>
+          <t>70591; 99059</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26542; 43458</t>
+          <t>26406; 43348</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>44235; 70451</t>
+          <t>44772; 70689</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52121; 80921</t>
+          <t>52235; 79231</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45045; 70679</t>
+          <t>44876; 69422</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24236; 37153</t>
+          <t>23509; 37201</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>116220; 155337</t>
+          <t>116772; 155087</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>135987; 177734</t>
+          <t>133847; 173258</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>123408; 162402</t>
+          <t>122806; 162112</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>52613; 75048</t>
+          <t>53280; 76239</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>108012; 141423</t>
+          <t>107432; 138636</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>68317; 99884</t>
+          <t>67328; 98536</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73211; 104354</t>
+          <t>74527; 105077</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>62371; 89222</t>
+          <t>61342; 88719</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>51015; 78067</t>
+          <t>50947; 78818</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>53888; 82745</t>
+          <t>54146; 82596</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58397; 87098</t>
+          <t>59102; 89195</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>38682; 58521</t>
+          <t>38512; 59256</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166413; 209564</t>
+          <t>165796; 209249</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>129923; 169935</t>
+          <t>128975; 171683</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>141283; 182249</t>
+          <t>141288; 181631</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>106411; 139515</t>
+          <t>106662; 140288</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>204518; 251896</t>
+          <t>203434; 254575</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>230841; 281727</t>
+          <t>228346; 281443</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>172859; 221375</t>
+          <t>173584; 222023</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>145050; 205504</t>
+          <t>146879; 202886</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>139384; 181712</t>
+          <t>139565; 183821</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>166240; 216745</t>
+          <t>166666; 214942</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>149358; 197776</t>
+          <t>150282; 197829</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>62261; 211564</t>
+          <t>73877; 209868</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>355484; 420527</t>
+          <t>355020; 423257</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>412483; 485830</t>
+          <t>408176; 480943</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>336975; 404221</t>
+          <t>337941; 403176</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>199352; 390634</t>
+          <t>204385; 392400</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>271394; 322418</t>
+          <t>270803; 322911</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>251617; 306187</t>
+          <t>252833; 307871</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>229046; 285657</t>
+          <t>227767; 282897</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>82444; 259735</t>
+          <t>82620; 260226</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>154791; 203734</t>
+          <t>156200; 203531</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>183752; 234855</t>
+          <t>186515; 235881</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>189432; 241509</t>
+          <t>189123; 239010</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>102976; 137799</t>
+          <t>103927; 137918</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>440606; 511718</t>
+          <t>440119; 511993</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>450066; 525310</t>
+          <t>448823; 523927</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>435702; 510983</t>
+          <t>432566; 506228</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>189365; 364962</t>
+          <t>183972; 365813</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1244842; 1361477</t>
+          <t>1252736; 1365380</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1206177; 1328041</t>
+          <t>1203028; 1319774</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1119083; 1234664</t>
+          <t>1118666; 1233119</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>665502; 926490</t>
+          <t>659122; 919495</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>785050; 885840</t>
+          <t>781070; 876985</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>902400; 1013655</t>
+          <t>905512; 1012153</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>870508; 975209</t>
+          <t>869521; 974405</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>525297; 713537</t>
+          <t>541235; 718797</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2055957; 2216426</t>
+          <t>2058038; 2217789</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2136501; 2303716</t>
+          <t>2142650; 2302854</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2015020; 2174439</t>
+          <t>2015671; 2174376</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1287875; 1605712</t>
+          <t>1274431; 1605487</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P23_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P23_R2-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,2; 43,64</t>
+          <t>31,23; 43,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,81; 44,28</t>
+          <t>33,19; 44,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,84; 42,29</t>
+          <t>31,08; 42,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,2; 33,18</t>
+          <t>19,15; 28,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,53; 30,7</t>
+          <t>19,71; 30,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,04; 39,6</t>
+          <t>27,46; 39,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,05; 30,79</t>
+          <t>20,55; 30,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,78; 26,64</t>
+          <t>17,92; 24,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,6; 35,76</t>
+          <t>27,55; 35,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,01; 40,52</t>
+          <t>32,12; 40,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,21; 35,11</t>
+          <t>27,36; 35,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,34; 29,22</t>
+          <t>19,27; 25,47</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,51; 40,46</t>
+          <t>31,25; 40,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,51; 44,13</t>
+          <t>35,62; 44,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,66; 45,95</t>
+          <t>37,5; 46,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,41; 31,88</t>
+          <t>20,89; 31,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,64; 26,13</t>
+          <t>18,89; 26,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,96; 32,16</t>
+          <t>23,93; 31,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,09; 31,4</t>
+          <t>23,38; 31,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,21; 22,68</t>
+          <t>15,99; 22,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,16; 31,9</t>
+          <t>26,44; 32,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,5; 36,43</t>
+          <t>29,86; 36,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,25; 37,11</t>
+          <t>31,17; 37,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,77; 25,82</t>
+          <t>19,52; 25,24</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,75; 48,24</t>
+          <t>37,14; 48,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,58; 44,84</t>
+          <t>33,2; 44,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,69; 35,73</t>
+          <t>25,36; 35,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,94; 28,0</t>
+          <t>20,54; 30,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,34; 32,86</t>
+          <t>23,2; 33,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,92; 30,7</t>
+          <t>20,15; 30,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,92; 29,15</t>
+          <t>19,72; 29,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,95; 22,12</t>
+          <t>14,75; 21,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,64; 39,1</t>
+          <t>31,66; 38,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,2; 35,55</t>
+          <t>27,94; 35,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,99; 30,73</t>
+          <t>23,75; 30,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,13; 23,81</t>
+          <t>18,78; 24,56</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,13; 50,33</t>
+          <t>40,11; 49,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,02; 36,78</t>
+          <t>26,46; 36,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,88; 43,34</t>
+          <t>32,93; 42,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,69; 31,12</t>
+          <t>19,0; 31,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,15; 31,04</t>
+          <t>22,29; 30,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,96; 31,0</t>
+          <t>21,91; 31,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,83; 33,08</t>
+          <t>23,83; 33,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,2; 20,59</t>
+          <t>15,35; 23,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,02; 39,25</t>
+          <t>32,16; 38,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25,63; 32,4</t>
+          <t>25,38; 32,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,21; 36,49</t>
+          <t>29,24; 36,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,7; 23,04</t>
+          <t>18,32; 25,51</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,61; 45,85</t>
+          <t>32,23; 45,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,42; 48,47</t>
+          <t>34,31; 49,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,42; 46,9</t>
+          <t>33,72; 46,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,77; 24,25</t>
+          <t>15,52; 25,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,56; 34,04</t>
+          <t>21,35; 34,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,79; 36,08</t>
+          <t>23,82; 36,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,53; 31,76</t>
+          <t>21,06; 32,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,27; 17,83</t>
+          <t>10,91; 17,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,41; 37,74</t>
+          <t>28,19; 37,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,97; 40,09</t>
+          <t>30,66; 40,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28,57; 37,72</t>
+          <t>28,8; 37,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,75; 19,68</t>
+          <t>14,32; 19,78</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,67; 51,19</t>
+          <t>39,97; 51,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,57; 35,96</t>
+          <t>24,54; 35,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,32; 39,93</t>
+          <t>27,54; 39,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,75; 32,9</t>
+          <t>23,25; 33,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,32; 28,34</t>
+          <t>18,18; 27,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,34; 29,5</t>
+          <t>19,22; 28,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,64; 32,66</t>
+          <t>21,47; 32,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,98; 23,05</t>
+          <t>15,12; 22,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30,2; 38,12</t>
+          <t>30,1; 37,9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23,28; 30,99</t>
+          <t>23,16; 30,75</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,35; 33,87</t>
+          <t>26,15; 34,27</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,25; 26,64</t>
+          <t>20,2; 26,59</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,08; 41,39</t>
+          <t>33,22; 40,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>34,45; 42,46</t>
+          <t>35,22; 42,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,48; 33,87</t>
+          <t>26,22; 33,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,57; 32,56</t>
+          <t>22,64; 30,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,87; 28,8</t>
+          <t>21,85; 28,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,02; 30,98</t>
+          <t>24,01; 30,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,8; 28,7</t>
+          <t>21,87; 28,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,74; 24,83</t>
+          <t>20,17; 25,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28,33; 33,77</t>
+          <t>28,6; 33,78</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,09; 35,45</t>
+          <t>30,31; 35,71</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25,13; 29,98</t>
+          <t>25,17; 30,19</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,92; 26,72</t>
+          <t>22,48; 27,17</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>36,41; 43,41</t>
+          <t>36,54; 43,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>32,49; 39,57</t>
+          <t>32,36; 39,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,25; 36,33</t>
+          <t>29,49; 36,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,91; 28,05</t>
+          <t>22,79; 29,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,94; 25,98</t>
+          <t>19,77; 25,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,67; 28,67</t>
+          <t>21,97; 28,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,89; 28,93</t>
+          <t>22,9; 29,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,48; 19,22</t>
+          <t>13,83; 18,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28,82; 33,52</t>
+          <t>28,68; 33,41</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28,04; 32,73</t>
+          <t>28,08; 33,02</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26,96; 31,55</t>
+          <t>26,99; 31,81</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,18; 22,23</t>
+          <t>19,32; 23,46</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>38,25; 41,68</t>
+          <t>38,16; 41,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35,12; 38,53</t>
+          <t>35,25; 38,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32,98; 36,35</t>
+          <t>33,22; 36,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,06; 26,59</t>
+          <t>24,02; 27,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23,11; 25,95</t>
+          <t>23,14; 26,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,46; 28,46</t>
+          <t>25,35; 28,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,57; 27,53</t>
+          <t>24,58; 27,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,79; 19,65</t>
+          <t>17,85; 20,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30,93; 33,33</t>
+          <t>30,98; 33,19</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30,69; 32,98</t>
+          <t>30,66; 33,0</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29,08; 31,37</t>
+          <t>29,14; 31,42</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,91; 22,56</t>
+          <t>21,06; 23,18</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84344</t>
+          <t>75950</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>65031</t>
+          <t>66333</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>149375</t>
+          <t>142284</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>87907; 119139</t>
+          <t>85271; 119582</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>96690; 130505</t>
+          <t>97820; 132066</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90606; 124241</t>
+          <t>91302; 125716</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66034; 103323</t>
+          <t>61060; 92437</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>50942; 80075</t>
+          <t>51420; 80356</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80556; 113738</t>
+          <t>78871; 114663</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60767; 88898</t>
+          <t>59321; 89324</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>54381; 77170</t>
+          <t>56641; 78816</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>147347; 190893</t>
+          <t>147095; 190519</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>186289; 235848</t>
+          <t>186941; 234753</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158516; 204488</t>
+          <t>159379; 204249</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>128251; 175631</t>
+          <t>122328; 161684</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133670</t>
+          <t>136735</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>99807</t>
+          <t>103279</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>233477</t>
+          <t>240014</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>155028; 199077</t>
+          <t>153771; 200389</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>174470; 223069</t>
+          <t>180061; 226806</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>183921; 230535</t>
+          <t>188166; 232082</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>110963; 165244</t>
+          <t>110841; 164787</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93952; 131694</t>
+          <t>95207; 132819</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>125472; 168456</t>
+          <t>125344; 165806</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>120289; 163533</t>
+          <t>121769; 161616</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83493; 116780</t>
+          <t>87384; 121322</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>260527; 317720</t>
+          <t>263305; 320679</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>313924; 374922</t>
+          <t>307396; 373416</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>319574; 379528</t>
+          <t>318730; 380696</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>204287; 266833</t>
+          <t>210228; 271827</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74218</t>
+          <t>79561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64222</t>
+          <t>64635</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>138439</t>
+          <t>144196</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>117184; 153800</t>
+          <t>118433; 153290</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>108827; 145311</t>
+          <t>107589; 143134</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81827; 113817</t>
+          <t>80774; 111823</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59875; 88508</t>
+          <t>64901; 95825</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>78280; 110217</t>
+          <t>77800; 111337</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71149; 104397</t>
+          <t>68517; 102405</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66983; 98032</t>
+          <t>66327; 98166</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>52181; 77235</t>
+          <t>52579; 76532</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>207027; 255813</t>
+          <t>207149; 254505</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>187291; 236096</t>
+          <t>185541; 236858</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>157093; 201232</t>
+          <t>155501; 200650</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>120589; 158363</t>
+          <t>126262; 165136</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76597</t>
+          <t>92572</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>73571</t>
+          <t>80223</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>150168</t>
+          <t>172796</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>143928; 180536</t>
+          <t>143869; 178776</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>101062; 137540</t>
+          <t>98961; 135736</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>121648; 160332</t>
+          <t>121819; 158063</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58406; 97273</t>
+          <t>70901; 117416</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>82288; 115301</t>
+          <t>82815; 113786</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>85416; 120556</t>
+          <t>85219; 121554</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>91976; 127693</t>
+          <t>91997; 128018</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43776; 97946</t>
+          <t>64784; 99381</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>233758; 286602</t>
+          <t>234817; 284495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>195505; 247175</t>
+          <t>193624; 244606</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>220847; 275846</t>
+          <t>221039; 274216</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>107978; 181652</t>
+          <t>145649; 202841</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33766</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29856</t>
+          <t>32172</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63622</t>
+          <t>73293</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>64267; 93207</t>
+          <t>65523; 92890</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73177; 103060</t>
+          <t>72957; 104416</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70591; 99059</t>
+          <t>71232; 98543</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26406; 43348</t>
+          <t>31912; 51507</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>44772; 70689</t>
+          <t>44331; 71968</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52235; 79231</t>
+          <t>52304; 79572</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44876; 69422</t>
+          <t>46029; 70083</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23509; 37201</t>
+          <t>24782; 40849</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>116772; 155087</t>
+          <t>115847; 154568</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>133847; 173258</t>
+          <t>132509; 175435</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>122806; 162112</t>
+          <t>123780; 160824</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>53280; 76239</t>
+          <t>62002; 85604</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>75056</t>
+          <t>75975</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>48078</t>
+          <t>48886</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>123134</t>
+          <t>124861</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>107432; 138636</t>
+          <t>108253; 138909</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>67328; 98536</t>
+          <t>67233; 98393</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74527; 105077</t>
+          <t>72465; 102633</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61342; 88719</t>
+          <t>62929; 90755</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>50947; 78818</t>
+          <t>50553; 76720</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54146; 82596</t>
+          <t>53824; 80585</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59102; 89195</t>
+          <t>58641; 88668</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>38512; 59256</t>
+          <t>39880; 59647</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>165796; 209249</t>
+          <t>165235; 208080</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>128975; 171683</t>
+          <t>128324; 170375</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>141288; 181631</t>
+          <t>140216; 183749</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>106662; 140288</t>
+          <t>107953; 142137</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>173018</t>
+          <t>190195</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>152222</t>
+          <t>176378</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>325240</t>
+          <t>366573</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>203434; 254575</t>
+          <t>204306; 252082</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>228346; 281443</t>
+          <t>233402; 284822</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>173584; 222023</t>
+          <t>171880; 220793</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>146879; 202886</t>
+          <t>162403; 216800</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>139565; 183821</t>
+          <t>139459; 184869</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>166666; 214942</t>
+          <t>166565; 215055</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>150282; 197829</t>
+          <t>150747; 195895</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>73877; 209868</t>
+          <t>154916; 199377</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>355020; 423257</t>
+          <t>358430; 423298</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>408176; 480943</t>
+          <t>411141; 484492</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>337941; 403176</t>
+          <t>338494; 406004</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>204385; 392400</t>
+          <t>334030; 403660</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>183841</t>
+          <t>209638</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>119160</t>
+          <t>135308</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>303001</t>
+          <t>344946</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>270803; 322911</t>
+          <t>271800; 324717</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>252833; 307871</t>
+          <t>251816; 306917</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>227767; 282897</t>
+          <t>229580; 284093</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>82620; 260226</t>
+          <t>181630; 235445</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>156200; 203531</t>
+          <t>154866; 202128</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>186515; 235881</t>
+          <t>180784; 235513</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>189123; 239010</t>
+          <t>189186; 243262</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>103927; 137918</t>
+          <t>114978; 155198</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>440119; 511993</t>
+          <t>437980; 510298</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>448823; 523927</t>
+          <t>449618; 528609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>432566; 506228</t>
+          <t>433127; 510548</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>183972; 365813</t>
+          <t>314624; 381992</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>834510</t>
+          <t>901748</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>651946</t>
+          <t>707214</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1486457</t>
+          <t>1608962</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1252736; 1365380</t>
+          <t>1249910; 1361442</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1203028; 1319774</t>
+          <t>1207570; 1324861</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1118666; 1233119</t>
+          <t>1127117; 1237940</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>659122; 919495</t>
+          <t>847849; 964672</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>781070; 876985</t>
+          <t>782094; 883362</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>905512; 1012153</t>
+          <t>901501; 1014393</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>869521; 974405</t>
+          <t>869748; 982473</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>541235; 718797</t>
+          <t>666059; 753555</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2058038; 2217789</t>
+          <t>2061715; 2208510</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2142650; 2302854</t>
+          <t>2140869; 2304193</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2015671; 2174376</t>
+          <t>2019716; 2177719</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1274431; 1605487</t>
+          <t>1528923; 1683254</t>
         </is>
       </c>
     </row>
